--- a/planering/biologi-omrade3/biologi-3-kahoot.xlsx
+++ b/planering/biologi-omrade3/biologi-3-kahoot.xlsx
@@ -1880,17 +1880,17 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
+          <t>Land, hav och luft</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Celler, vävnader och organ</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
           <t>Riken, släkten och arter</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Land, hav och luft</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>Celler, vävnader och organ</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
+          <t>Ekosystem</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Släkte</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
           <t>Biotop</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Population</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Ekosystem</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>Släkte</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1989,22 +1989,22 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
+          <t>Hur gamla arterna är</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Hur stora arterna är</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Antalet olika arter i ett område</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
           <t>Antalet individer av en art</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>Hur stora arterna är</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Antalet olika arter i ett område</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>Hur gamla arterna är</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
+          <t>Arterna är större</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
           <t>Det finns färre rovdjur</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Arterna är större</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
+          <t>Potatisen var för varm</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
           <t>Det fanns för många olika sorter</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Potatisen var för varm</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -2160,22 +2160,22 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
+          <t>Biotiska, abiotiska, ekologiska och sociala</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Försörjande, reglerande, stödjande och kulturella</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
           <t>Gröna, blå, vita och svarta</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Försörjande, reglerande, stödjande och kulturella</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>Producerande, nedbrytande, konsumerande och skyddande</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>Biotiska, abiotiska, ekologiska och sociala</t>
         </is>
       </c>
       <c r="G14" s="14" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
+          <t>Fotosyntes</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Jäsning</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Pollinering</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
           <t>Nedbrytning</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Fotosyntes</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Pollinering</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>Jäsning</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
+          <t>Att fotografera natur</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
           <t>Att sälja timmer</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Att fotografera natur</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
+          <t>En lista över farliga arter för människor</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
           <t>En lista över arter man får jaga</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>En lista över farliga arter för människor</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2673,22 +2673,22 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
+          <t>En växt utan rötter</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
           <t>En bakterie som bryter ner löv</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Samlevnad mellan en svamp och en alg eller bakterie som gör fotosyntes</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>En sorts mossa</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Samlevnad mellan en svamp och en alg eller bakterie som gör fotosyntes</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>En växt utan rötter</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
+          <t>Bara artens namn</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
           <t>Ett svenskt ord</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>Bara artens namn</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
@@ -2792,17 +2792,17 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
+          <t>En karta över arters utbredning</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>En metod för att räkna celler</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
           <t>En lista över rödlistade arter</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>En karta över arters utbredning</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>En metod för att räkna celler</t>
         </is>
       </c>
       <c r="G25" s="14" t="n">
@@ -2844,17 +2844,17 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
+          <t>Ett val som individen gör varje dag</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Ett drag som gör att en art klarar sin miljö</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
           <t>En sjukdom hos arten</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Ett drag som gör att en art klarar sin miljö</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>Ett val som individen gör varje dag</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2906,17 +2906,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Variation</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
           <t>Konkurrens</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Variation</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>Population</t>
         </is>
       </c>
       <c r="G27" s="14" t="n">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
+          <t>Antibiotikan blir svagare av sig själv</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
           <t>Bakterierna blir större</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Antibiotikan blir svagare av sig själv</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
